--- a/data/trans_camb/P19C09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C09-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,18</t>
+          <t>-3,45; 2,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,46</t>
+          <t>-0,59; 5,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 8,85</t>
+          <t>0,15; 9,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,21</t>
+          <t>-2,24; 5,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,09</t>
+          <t>-0,57; 4,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,32</t>
+          <t>-0,81; 4,21</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 290,0</t>
+          <t>-94,38; 500,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 573,5</t>
+          <t>-23,22; 746,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 545,94</t>
+          <t>-4,12; 776,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,74; 316,99</t>
+          <t>-55,28; 360,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 321,05</t>
+          <t>-18,06; 294,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 270,02</t>
+          <t>-23,49; 270,05</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; -0,16</t>
+          <t>-4,4; -0,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,84</t>
+          <t>-3,16; 1,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,42</t>
+          <t>-3,25; 1,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -0,13</t>
+          <t>-3,9; -0,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,03</t>
+          <t>-3,27; -0,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,23</t>
+          <t>-3,12; 0,28</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-90,56; 15,98</t>
+          <t>-89,25; 8,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,91; 88,89</t>
+          <t>-70,36; 102,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,47; 59,56</t>
+          <t>-75,75; 61,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,86; 11,45</t>
+          <t>-88,65; 4,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,22; 6,28</t>
+          <t>-76,11; 1,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,86; 11,74</t>
+          <t>-70,22; 15,93</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,5</t>
+          <t>-2,88; 1,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,91</t>
+          <t>-3,19; 0,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,85</t>
+          <t>-4,25; 1,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,1</t>
+          <t>-5,55; 0,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,11</t>
+          <t>-2,76; 0,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -0,12</t>
+          <t>-3,7; -0,22</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,71; 309,59</t>
+          <t>-87,34; 332,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 246,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 91,29</t>
+          <t>-75,48; 74,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-94,66; 60,68</t>
+          <t>-93,15; 78,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,2; 57,86</t>
+          <t>-65,03; 56,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,14; 4,78</t>
+          <t>-87,67; 4,27</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 3,1</t>
+          <t>-3,65; 3,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 6,86</t>
+          <t>-0,68; 7,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,07</t>
+          <t>-2,05; 3,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,8</t>
+          <t>-1,12; 5,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,37</t>
+          <t>-2,19; 2,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,02</t>
+          <t>0,21; 4,88</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-71,55; 188,29</t>
+          <t>-68,48; 217,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 430,61</t>
+          <t>-20,19; 374,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 241,51</t>
+          <t>-47,88; 198,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,61; 253,23</t>
+          <t>-31,24; 256,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 107,59</t>
+          <t>-47,41; 102,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 230,46</t>
+          <t>4,3; 222,69</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 1,82</t>
+          <t>-5,21; 1,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 5,41</t>
+          <t>-3,59; 5,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 2,88</t>
+          <t>-3,89; 2,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 6,24</t>
+          <t>-1,88; 6,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,61</t>
+          <t>-3,39; 1,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 4,2</t>
+          <t>-1,81; 4,11</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 143,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,02; 318,62</t>
+          <t>-78,16; 274,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 331,97</t>
+          <t>-100,0; 399,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 528,04</t>
+          <t>-53,6; 527,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-79,33; 100,07</t>
+          <t>-78,81; 92,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 210,23</t>
+          <t>-42,6; 224,57</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,79</t>
+          <t>-3,57; 1,57</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,59</t>
+          <t>-4,51; 0,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,1</t>
+          <t>-2,73; 3,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 2,62</t>
+          <t>-3,72; 2,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,01</t>
+          <t>-2,06; 2,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,86</t>
+          <t>-2,96; 0,84</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 306,8</t>
+          <t>-100,0; 216,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 404,1</t>
+          <t>-71,14; 417,96</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-82,1; 378,74</t>
+          <t>-86,12; 248,07</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 166,1</t>
+          <t>-60,87; 160,11</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,95; 90,94</t>
+          <t>-81,12; 81,23</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,96</t>
+          <t>-1,83; 1,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,23</t>
+          <t>-2,14; 2,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,01</t>
+          <t>-4,69; -0,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,73</t>
+          <t>-3,91; 0,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,16</t>
+          <t>-2,66; 0,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,89</t>
+          <t>-2,45; 0,93</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,88; 171,44</t>
+          <t>-59,59; 145,07</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,75; 143,4</t>
+          <t>-67,77; 160,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-76,39; 2,59</t>
+          <t>-78,67; -1,11</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-68,02; 29,42</t>
+          <t>-68,45; 34,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,46; 10,73</t>
+          <t>-60,87; 17,91</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 32,98</t>
+          <t>-55,54; 40,57</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,32</t>
+          <t>-2,92; -0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,53</t>
+          <t>-1,79; 1,38</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,81</t>
+          <t>-2,09; 0,83</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,23</t>
+          <t>-1,78; 1,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,11</t>
+          <t>-1,84; 0,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,94</t>
+          <t>-1,18; 0,96</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 58,96</t>
+          <t>-93,57; 19,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-62,14; 122,25</t>
+          <t>-63,3; 106,79</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 111,77</t>
+          <t>-76,06; 104,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-67,37; 140,84</t>
+          <t>-69,94; 142,11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-74,64; 21,99</t>
+          <t>-73,75; 30,87</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-50,48; 74,38</t>
+          <t>-47,83; 80,05</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,8; -0,13</t>
+          <t>-1,75; -0,09</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,15</t>
+          <t>-0,71; 1,29</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,59</t>
+          <t>-1,27; 0,54</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,38</t>
+          <t>-1,37; 0,42</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,23; -0,04</t>
+          <t>-1,22; 0,01</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,46</t>
+          <t>-0,71; 0,53</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-57,34; -4,59</t>
+          <t>-56,35; -2,49</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 51,5</t>
+          <t>-23,79; 59,45</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 22,96</t>
+          <t>-34,6; 20,59</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 14,71</t>
+          <t>-39,36; 16,09</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-37,9; -0,88</t>
+          <t>-38,31; 0,43</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 17,95</t>
+          <t>-22,34; 21,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C09-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,13</t>
+          <t>-3,3; 2,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 5,7</t>
+          <t>-0,95; 5,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 9,31</t>
+          <t>0,27; 9,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 5,19</t>
+          <t>-2,36; 5,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,64</t>
+          <t>-0,84; 4,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,21</t>
+          <t>-0,84; 4,05</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-94,38; 500,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 746,22</t>
+          <t>-35,08; 673,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 776,34</t>
+          <t>-8,41; 666,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 360,08</t>
+          <t>-52,09; 433,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 294,33</t>
+          <t>-23,38; 290,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 270,05</t>
+          <t>-27,24; 240,93</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; -0,08</t>
+          <t>-4,55; -0,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,86</t>
+          <t>-3,38; 1,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,23</t>
+          <t>-3,37; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,04</t>
+          <t>-4,2; -0,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,05</t>
+          <t>-3,23; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,28</t>
+          <t>-2,94; 0,29</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-89,25; 8,84</t>
+          <t>-89,34; 15,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,36; 102,61</t>
+          <t>-69,76; 106,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,75; 61,27</t>
+          <t>-75,09; 66,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,65; 4,66</t>
+          <t>-87,08; 16,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 1,59</t>
+          <t>-74,48; -0,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,22; 15,93</t>
+          <t>-68,93; 16,34</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,58</t>
+          <t>-3,26; 1,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,88</t>
+          <t>-3,67; 0,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 1,65</t>
+          <t>-3,91; 2,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 0,08</t>
+          <t>-5,53; 0,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,93</t>
+          <t>-2,68; 1,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,22</t>
+          <t>-3,63; -0,04</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,34; 332,91</t>
+          <t>-100,0; 219,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 246,9</t>
+          <t>-100,0; 158,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,48; 74,64</t>
+          <t>-70,31; 114,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-93,15; 78,78</t>
+          <t>-93,75; 38,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 56,29</t>
+          <t>-65,2; 60,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,67; 4,27</t>
+          <t>-87,02; 16,09</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,04</t>
+          <t>-3,73; 3,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 7,08</t>
+          <t>-0,57; 6,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,67</t>
+          <t>-2,24; 3,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 5,16</t>
+          <t>-1,28; 5,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,29</t>
+          <t>-2,05; 2,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,88</t>
+          <t>0,13; 5,03</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 217,41</t>
+          <t>-71,72; 167,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 374,25</t>
+          <t>-19,45; 362,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,88; 198,72</t>
+          <t>-53,45; 197,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 256,5</t>
+          <t>-32,18; 262,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,41; 102,56</t>
+          <t>-46,38; 101,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 222,69</t>
+          <t>0,52; 226,84</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 1,73</t>
+          <t>-5,27; 1,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 5,12</t>
+          <t>-4,16; 5,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,93</t>
+          <t>-3,79; 3,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 6,37</t>
+          <t>-1,65; 6,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,44</t>
+          <t>-3,42; 1,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,11</t>
+          <t>-1,49; 4,7</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 143,17</t>
+          <t>-100,0; 175,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 274,06</t>
+          <t>-83,2; 326,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 399,89</t>
+          <t>-100,0; 440,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-53,6; 527,18</t>
+          <t>-49,13; 596,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-78,81; 92,81</t>
+          <t>-80,37; 113,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 224,57</t>
+          <t>-41,67; 234,85</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,57</t>
+          <t>-3,75; 1,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,6</t>
+          <t>-4,45; 0,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,87</t>
+          <t>-2,37; 3,92</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,32</t>
+          <t>-3,34; 2,48</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,14</t>
+          <t>-2,3; 2,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,84</t>
+          <t>-3,08; 0,75</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 216,75</t>
+          <t>-86,92; 268,29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 417,96</t>
+          <t>-65,15; 390,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-86,12; 248,07</t>
+          <t>-83,24; 329,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 160,11</t>
+          <t>-60,93; 174,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-81,12; 81,23</t>
+          <t>-81,35; 74,88</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,92</t>
+          <t>-2,14; 1,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 2,11</t>
+          <t>-1,99; 2,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -0,13</t>
+          <t>-4,53; -0,16</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,93</t>
+          <t>-3,74; 1,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,39</t>
+          <t>-2,61; 0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,93</t>
+          <t>-2,29; 0,73</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-59,59; 145,07</t>
+          <t>-61,56; 139,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,77; 160,99</t>
+          <t>-64,55; 158,85</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-78,67; -1,11</t>
+          <t>-76,18; 2,46</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-68,45; 34,15</t>
+          <t>-66,72; 35,49</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 17,91</t>
+          <t>-61,21; 10,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 40,57</t>
+          <t>-55,22; 28,37</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,92; -0,0</t>
+          <t>-2,92; 0,1</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,38</t>
+          <t>-1,68; 1,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,83</t>
+          <t>-1,95; 0,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,23</t>
+          <t>-1,75; 1,25</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,2</t>
+          <t>-1,96; 0,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,96</t>
+          <t>-1,31; 1,07</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-93,57; 19,82</t>
+          <t>-91,62; 46,05</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 106,79</t>
+          <t>-58,7; 122,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-76,06; 104,01</t>
+          <t>-75,62; 116,33</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 142,11</t>
+          <t>-70,41; 137,29</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 30,87</t>
+          <t>-76,3; 10,85</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-47,83; 80,05</t>
+          <t>-51,21; 75,91</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,09</t>
+          <t>-1,7; -0,04</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,29</t>
+          <t>-0,74; 1,19</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,54</t>
+          <t>-1,23; 0,62</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,42</t>
+          <t>-1,42; 0,4</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,01</t>
+          <t>-1,32; -0,0</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,53</t>
+          <t>-0,81; 0,5</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-56,35; -2,49</t>
+          <t>-53,94; 0,68</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 59,45</t>
+          <t>-24,78; 53,31</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-34,6; 20,59</t>
+          <t>-33,47; 23,9</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 16,09</t>
+          <t>-38,51; 16,39</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 0,43</t>
+          <t>-39,49; -0,11</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 21,09</t>
+          <t>-25,28; 19,99</t>
         </is>
       </c>
     </row>
